--- a/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
@@ -553,66 +553,66 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E2" t="n">
-        <v>960</v>
+        <v>1180</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3077269933674377</v>
+        <v>0.2430222915463953</v>
       </c>
       <c r="H2" t="n">
-        <v>426.7361442702318</v>
+        <v>378.8305795828101</v>
       </c>
       <c r="I2" t="n">
-        <v>9.971253084328792e-79</v>
+        <v>2.142744421722969e-73</v>
       </c>
       <c r="J2" t="n">
-        <v>110.0735669101074</v>
+        <v>138.3668153787242</v>
       </c>
       <c r="K2" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L2" t="n">
-        <v>48.92955159301106</v>
+        <v>44.42167869910998</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1146599655313619</v>
+        <v>0.1172600130328171</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.7486643282984455, 'N1ratio-ArgsPreds': -0.2076128570460793}</t>
+          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 3.609420076864592e-116, 'N1ratio-ArgsPreds': 9.971253084334582e-79}</t>
+          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5547314605892099}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892107)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5547314605892106)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(30.772699336743898)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -632,76 +632,76 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E3" t="n">
-        <v>959</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.309932915807294</v>
+        <v>0.243029434005724</v>
       </c>
       <c r="H3" t="n">
-        <v>215.3599795351147</v>
+        <v>189.2621163653774</v>
       </c>
       <c r="I3" t="n">
-        <v>5.602530738922377e-78</v>
+        <v>5.212741901581616e-72</v>
       </c>
       <c r="J3" t="n">
-        <v>109.7228183629943</v>
+        <v>138.3655098193395</v>
       </c>
       <c r="K3" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L3" t="n">
-        <v>24.64015007006211</v>
+        <v>22.21149212924733</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1144137834859169</v>
+        <v>0.1173583628662761</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.7367253482977725, 'N1ratio-ArgsPreds': -0.2130532914365536, 'Fam_class': 0.0006058329789900769}</t>
+          <t>{'const': 0.5846789005586817, 'N1ratio-ArgsPreds': -2.2040046619576232, 'Fam_class': -2.8987753571532647e-05}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 1.0006382299714886e-108, 'N1ratio-ArgsPreds': 2.495655154958191e-76, 'Fam_class': 0.08028464407536798}</t>
+          <t>{'const': 9.50841278385966e-109, 'N1ratio-ArgsPreds': 1.1808755686741504e-67, 'Fam_class': 0.916018435400811}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5692680367849594, 'Fam_class': 0.04916537895054843}</t>
+          <t>{'N1ratio-ArgsPreds': -0.49214788769884166, 'Fam_class': -0.002796984756003274}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5477183770250377), 'Fam_class': np.float64(0.05644902179184039)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4754845360853714), 'Fam_class': np.float64(-0.0030717250736025897)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5438166849754508), 'Fam_class': np.float64(0.04696724858724697)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47025066037116536), 'Fam_class': np.float64(-0.00267253799384983)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(29.573658685768866), 'Fam_class': np.float64(0.22059224398562524)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.11356835795171), 'Fam_class': np.float64(0.0007142459328570874)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.002205922439856289</v>
+        <v>7.142459328646211e-06</v>
       </c>
       <c r="V3" t="n">
-        <v>3.065614442829183</v>
+        <v>0.01112455348566031</v>
       </c>
       <c r="W3" t="n">
-        <v>0.08028464407538698</v>
+        <v>0.9160184354065133</v>
       </c>
     </row>
     <row r="4">
@@ -713,80 +713,80 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class']</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E4" t="n">
-        <v>956</v>
+        <v>1178</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4796152051467759</v>
+        <v>0.356995974088077</v>
       </c>
       <c r="H4" t="n">
-        <v>176.2204202179437</v>
+        <v>218.0086181572158</v>
       </c>
       <c r="I4" t="n">
-        <v>6.655474998894777e-133</v>
+        <v>1.789150003397271e-112</v>
       </c>
       <c r="J4" t="n">
-        <v>82.74280520326819</v>
+        <v>117.5337375824251</v>
       </c>
       <c r="K4" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L4" t="n">
-        <v>15.25206265997006</v>
+        <v>21.75158549846971</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08655105146785376</v>
+        <v>0.09977397078304334</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.5022521165134575, 'N1ratio-ArgsPreds': -0.18685962287250713, 'Fam_class': -6.335276171802039e-05, 'latitude': 0.0038619116753522, 'longitude': -0.0011726761380343907, 'Macro_class': 0.10605541705456369}</t>
+          <t>{'const': 0.41595982391072817, 'N1ratio-ArgsPreds': -2.241457698387184, 'Fam_class': 0.00015368108675852297, 'Macro_class': 0.07804745806789959}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 5.8731439146720054e-58, 'N1ratio-ArgsPreds': 1.0211007272848054e-63, 'Fam_class': 0.8394246983394338, 'latitude': 1.8474541409505307e-09, 'longitude': 1.8907031549356204e-11, 'Macro_class': 4.467737364812793e-48}</t>
+          <t>{'const': 6.599951616324121e-57, 'N1ratio-ArgsPreds': 7.07156264147149e-80, 'Fam_class': 0.5448322963978546, 'Macro_class': 1.0857045464293654e-43}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4992798278297781, 'Fam_class': -0.005141289176139894, 'latitude': 0.1558916288264876, 'longitude': -0.22038612469956442, 'Macro_class': 0.4370054318476467}</t>
+          <t>{'N1ratio-ArgsPreds': -0.5005110427705484, 'Fam_class': 0.014828456985771132, 'Macro_class': 0.33802393293067784}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5070534211241643), 'Fam_class': np.float64(-0.006555147159176553), 'latitude': np.float64(0.19262632455537154), 'longitude': np.float64(-0.21467307872353028), 'Macro_class': np.float64(0.4462948780478797)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5121172767786027), 'Fam_class': np.float64(0.017644751553077983), 'Macro_class': np.float64(0.38801559902695193)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4243769277564699), 'Fam_class': np.float64(-0.004728834077302492), 'latitude': np.float64(0.1416082152282898), 'longitude': np.float64(-0.15855682404396165), 'Macro_class': np.float64(0.35976300929901456)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47810778584269736), 'Fam_class': np.float64(0.014151093818749218), 'Macro_class': np.float64(0.3375893068246497)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.009577681202007), 'Fam_class': np.float64(0.0022361871730657307), 'latitude': np.float64(2.0052886620141654), 'longitude': np.float64(2.5140266450907816), 'Macro_class': np.float64(12.942942285988284)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(22.858705488340654), 'Fam_class': np.float64(0.02002534562670423), 'Macro_class': np.float64(11.396654008234748)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1696822893394819</v>
+        <v>0.1139665400823531</v>
       </c>
       <c r="V4" t="n">
-        <v>103.9078967544253</v>
+        <v>208.7896479755502</v>
       </c>
       <c r="W4" t="n">
-        <v>3.179629592550573e-58</v>
+        <v>1.085704546429936e-43</v>
       </c>
     </row>
     <row r="5">
@@ -798,80 +798,80 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['N1ratio-ArgsPreds', 'Fam_class', 'latitude', 'longitude', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
+          <t>['N1ratio-ArgsPreds', 'Fam_class', 'Macro_class', 'Nlen_freq', 'Vlen_freq']</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>962</v>
+        <v>1182</v>
       </c>
       <c r="E5" t="n">
-        <v>954</v>
+        <v>1176</v>
       </c>
       <c r="F5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4899845368979755</v>
+        <v>0.3608503965538554</v>
       </c>
       <c r="H5" t="n">
-        <v>130.9330744482489</v>
+        <v>132.7889633535823</v>
       </c>
       <c r="I5" t="n">
-        <v>8.390176564638851e-135</v>
+        <v>1.158898468227764e-111</v>
       </c>
       <c r="J5" t="n">
-        <v>81.09404911803406</v>
+        <v>116.8291935043657</v>
       </c>
       <c r="K5" t="n">
-        <v>159.0031185031185</v>
+        <v>182.7884940778342</v>
       </c>
       <c r="L5" t="n">
-        <v>11.12986705501206</v>
+        <v>13.1918601146937</v>
       </c>
       <c r="M5" t="n">
-        <v>0.08500424435852627</v>
+        <v>0.09934455229963067</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1654558985464292</v>
+        <v>0.1547743387619256</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.34837678341195283, 'N1ratio-ArgsPreds': -0.17110226205503745, 'Fam_class': -0.0006149714696248247, 'latitude': 0.004130703479984761, 'longitude': -0.0013150306758518528, 'Macro_class': 0.10009547794010439, 'Nlen_freq': -0.01820089026954686, 'Vlen_freq': 0.04449842893550022}</t>
+          <t>{'const': 0.408076952072044, 'N1ratio-ArgsPreds': -2.156788804960891, 'Fam_class': -0.00010875434157321574, 'Macro_class': 0.07213034190350337, 'Nlen_freq': -0.26538283520756023, 'Vlen_freq': 0.40149771472974777}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 1.3508935437592607e-06, 'N1ratio-ArgsPreds': 2.0118916735885443e-50, 'Fam_class': 0.06712240191055562, 'latitude': 1.547343676620687e-10, 'longitude': 2.959470337716521e-13, 'Macro_class': 9.06208432530112e-40, 'Nlen_freq': 0.26824614531785745, 'Vlen_freq': 0.00044341186477896377}</t>
+          <t>{'const': 2.2596589821426198e-21, 'N1ratio-ArgsPreds': 4.502887017879908e-70, 'Fam_class': 0.6893973889406835, 'Macro_class': 3.874576589349592e-33, 'Nlen_freq': 0.08773693996979143, 'Vlen_freq': 0.00946288752899593}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.45717692579531466, 'Fam_class': -0.04990699812724361, 'latitude': 0.16674179728238828, 'longitude': -0.2471394318620813, 'Macro_class': 0.41244727311484014, 'Nlen_freq': -0.04303296638783081, 'Vlen_freq': 0.14925359587953826}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4816047229370245, 'Fam_class': -0.010493542894892722, 'Macro_class': 0.3123968731005315, 'Nlen_freq': -0.06622671289629897, 'Vlen_freq': 0.10950154803404281}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.45665248542155434), 'Fam_class': np.float64(-0.05923953233639515), 'latitude': np.float64(0.20507553709001963), 'longitude': np.float64(-0.23302575735888376), 'Macro_class': np.float64(0.4086019713193207), 'Nlen_freq': np.float64(-0.035841901011898804), 'Vlen_freq': np.float64(0.11339379054556382)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48359277861673633), 'Fam_class': np.float64(-0.011656782888603237), 'Macro_class': np.float64(0.3393596909691059), 'Nlen_freq': np.float64(-0.049770210315821586), 'Vlen_freq': np.float64(0.07557554484528194)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.366573172409678), 'Fam_class': np.float64(-0.04238055824704733), 'latitude': np.float64(0.14963578392178165), 'longitude': np.float64(-0.17112723603357485), 'Macro_class': np.float64(0.3197113447403146), 'Nlen_freq': np.float64(-0.025613082221553094), 'Vlen_freq': np.float64(0.08150629710826814)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.44170016365105674), 'Fam_class': np.float64(-0.00931986191210442), 'Macro_class': np.float64(0.28842331961400464), 'Nlen_freq': np.float64(-0.03983907946456676), 'Vlen_freq': np.float64(0.06059354704630172)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(13.437589073049553), 'Fam_class': np.float64(0.17961117173313718), 'latitude': np.float64(2.2390867829886125), 'longitude': np.float64(2.928453091249084), 'Macro_class': np.float64(10.221534395566028), 'Nlen_freq': np.float64(0.06560299808880392), 'Vlen_freq': np.float64(0.6643276468301279)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(19.50990345693703), 'Fam_class': np.float64(0.008685982606069466), 'Macro_class': np.float64(8.318801129716228), 'Nlen_freq': np.float64(0.15871522525840648), 'Vlen_freq': np.float64(0.36715779436523793)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.01036933175119958</v>
+        <v>0.003854422465778384</v>
       </c>
       <c r="V5" t="n">
-        <v>9.698080946876624</v>
+        <v>3.545962318771366</v>
       </c>
       <c r="W5" t="n">
-        <v>6.767394114055434e-05</v>
+        <v>0.02914962989155186</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2430222915463953</v>
+        <v>0.2355842238404511</v>
       </c>
       <c r="H2" t="n">
-        <v>378.8305795828101</v>
+        <v>363.662541775839</v>
       </c>
       <c r="I2" t="n">
-        <v>2.142744421722969e-73</v>
+        <v>6.968483886006474e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.3668153787242</v>
+        <v>138.7796194903806</v>
       </c>
       <c r="K2" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>44.42167869910998</v>
+        <v>42.7702959072505</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1172600130328171</v>
+        <v>0.1176098470257463</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5838997183381505, 'N1ratio-ArgsPreds': -2.2076993978570845}</t>
+          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 7.775219821683825e-118, 'N1ratio-ArgsPreds': 2.142744421721985e-73}</t>
+          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49297291157465767}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.49297291157465845)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(24.3022291546396)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.243029434005724</v>
+        <v>0.2357097723163037</v>
       </c>
       <c r="H3" t="n">
-        <v>189.2621163653774</v>
+        <v>181.8038563721716</v>
       </c>
       <c r="I3" t="n">
-        <v>5.212741901581616e-72</v>
+        <v>1.516253387259223e-69</v>
       </c>
       <c r="J3" t="n">
-        <v>138.3655098193395</v>
+        <v>138.7568261752113</v>
       </c>
       <c r="K3" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>22.21149212924733</v>
+        <v>21.39654461120992</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1173583628662761</v>
+        <v>0.117690268172359</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5846789005586817, 'N1ratio-ArgsPreds': -2.2040046619576232, 'Fam_class': -2.8987753571532647e-05}</t>
+          <t>{'const': 0.5715863027053953, 'N1ratio-ArgsPreds': -2.1038747852921906, 'Fam_class': -0.00012087906762604605}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 9.50841278385966e-109, 'N1ratio-ArgsPreds': 1.1808755686741504e-67, 'Fam_class': 0.916018435400811}</t>
+          <t>{'const': 3.187628831203141e-106, 'N1ratio-ArgsPreds': 5.885558436980357e-65, 'Fam_class': 0.6599584798021098}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.49214788769884166, 'Fam_class': -0.002796984756003274}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48199152199736595, 'Fam_class': -0.011703157297484928}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4754845360853714), 'Fam_class': np.float64(-0.0030717250736025897)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4668105918264926), 'Fam_class': np.float64(-0.012815657774598577)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47025066037116536), 'Fam_class': np.float64(-0.00267253799384983)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46146851927307075), 'Fam_class': np.float64(-0.011204841625506699)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.11356835795171), 'Fam_class': np.float64(0.0007142459328570874)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.295319428008046), 'Fam_class': np.float64(0.012554847585268758)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>7.142459328646211e-06</v>
+        <v>0.0001255484758526659</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01112455348566031</v>
+        <v>0.1936720471736194</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9160184354065133</v>
+        <v>0.659958479806684</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.356995974088077</v>
+        <v>0.3492609714554959</v>
       </c>
       <c r="H4" t="n">
-        <v>218.0086181572158</v>
+        <v>210.7498327938573</v>
       </c>
       <c r="I4" t="n">
-        <v>1.789150003397271e-112</v>
+        <v>2.026215300087851e-109</v>
       </c>
       <c r="J4" t="n">
-        <v>117.5337375824251</v>
+        <v>118.1416155781914</v>
       </c>
       <c r="K4" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>21.75158549846971</v>
+        <v>21.13609993981325</v>
       </c>
       <c r="M4" t="n">
-        <v>0.09977397078304334</v>
+        <v>0.1002899962463424</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.41595982391072817, 'N1ratio-ArgsPreds': -2.241457698387184, 'Fam_class': 0.00015368108675852297, 'Macro_class': 0.07804745806789959}</t>
+          <t>{'const': 0.4028340233159108, 'N1ratio-ArgsPreds': -2.1345183214926675, 'Fam_class': 5.63257260560442e-05, 'Macro_class': 0.07763441457018583}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 6.599951616324121e-57, 'N1ratio-ArgsPreds': 7.07156264147149e-80, 'Fam_class': 0.5448322963978546, 'Macro_class': 1.0857045464293654e-43}</t>
+          <t>{'const': 3.839914156116589e-54, 'N1ratio-ArgsPreds': 2.675478655394602e-76, 'Fam_class': 0.8244469015918944, 'Macro_class': 4.322341342706756e-43}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.5005110427705484, 'Fam_class': 0.014828456985771132, 'Macro_class': 0.33802393293067784}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4890118659626547, 'Fam_class': 0.005453291830213405, 'Macro_class': 0.33738002947098594}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5121172767786027), 'Fam_class': np.float64(0.017644751553077983), 'Macro_class': np.float64(0.38801559902695193)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.5018946891585374), 'Fam_class': np.float64(0.006464479485016144), 'Macro_class': np.float64(0.38544880990627617)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47810778584269736), 'Fam_class': np.float64(0.014151093818749218), 'Macro_class': np.float64(0.3375893068246497)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4680968305790246), 'Fam_class': np.float64(0.005214900944498913), 'Macro_class': np.float64(0.33697358819231116)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(22.858705488340654), 'Fam_class': np.float64(0.02002534562670423), 'Macro_class': np.float64(11.396654008234748)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.911464279812808), 'Fam_class': np.float64(0.002719519186093565), 'Macro_class': np.float64(11.35511991392013)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1139665400823531</v>
+        <v>0.1135511991391922</v>
       </c>
       <c r="V4" t="n">
-        <v>208.7896479755502</v>
+        <v>205.5560012823487</v>
       </c>
       <c r="W4" t="n">
-        <v>1.085704546429936e-43</v>
+        <v>4.322341342706068e-43</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3608503965538554</v>
+        <v>0.3545170942653388</v>
       </c>
       <c r="H5" t="n">
-        <v>132.7889633535823</v>
+        <v>129.1783559725805</v>
       </c>
       <c r="I5" t="n">
-        <v>1.158898468227764e-111</v>
+        <v>3.719729292359789e-109</v>
       </c>
       <c r="J5" t="n">
-        <v>116.8291935043657</v>
+        <v>117.1873669267449</v>
       </c>
       <c r="K5" t="n">
-        <v>182.7884940778342</v>
+        <v>181.5499153976311</v>
       </c>
       <c r="L5" t="n">
-        <v>13.1918601146937</v>
+        <v>12.87250969417726</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09934455229963067</v>
+        <v>0.09964912153634767</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1547743387619256</v>
+        <v>0.1537255845873253</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.408076952072044, 'N1ratio-ArgsPreds': -2.156788804960891, 'Fam_class': -0.00010875434157321574, 'Macro_class': 0.07213034190350337, 'Nlen_freq': -0.26538283520756023, 'Vlen_freq': 0.40149771472974777}</t>
+          <t>{'const': 0.4066187961530553, 'N1ratio-ArgsPreds': -2.0417210982057163, 'Fam_class': -0.00023527710716809958, 'Macro_class': 0.07082281520305496, 'Nlen_freq': -0.34722273935809433, 'Vlen_freq': 0.4723770185218674}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 2.2596589821426198e-21, 'N1ratio-ArgsPreds': 4.502887017879908e-70, 'Fam_class': 0.6893973889406835, 'Macro_class': 3.874576589349592e-33, 'Nlen_freq': 0.08773693996979143, 'Vlen_freq': 0.00946288752899593}</t>
+          <t>{'const': 3.460694618048324e-21, 'N1ratio-ArgsPreds': 1.365843532947458e-66, 'Fam_class': 0.38608704188315124, 'Macro_class': 4.657879342781081e-32, 'Nlen_freq': 0.024814696161224423, 'Vlen_freq': 0.0021229591976609477}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4816047229370245, 'Fam_class': -0.010493542894892722, 'Macro_class': 0.3123968731005315, 'Nlen_freq': -0.06622671289629897, 'Vlen_freq': 0.10950154803404281}</t>
+          <t>{'N1ratio-ArgsPreds': -0.46775229519262185, 'Fam_class': -0.02277884043748356, 'Macro_class': 0.3077784976252147, 'Nlen_freq': -0.08706200994837242, 'Vlen_freq': 0.12957205861125248}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48359277861673633), 'Fam_class': np.float64(-0.011656782888603237), 'Macro_class': np.float64(0.3393596909691059), 'Nlen_freq': np.float64(-0.049770210315821586), 'Vlen_freq': np.float64(0.07557554484528194)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.47262480075837676), 'Fam_class': np.float64(-0.02527585041960119), 'Macro_class': np.float64(0.33382556693384297), 'Nlen_freq': np.float64(-0.06538824844991198), 'Vlen_freq': np.float64(0.08943443504502634)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.44170016365105674), 'Fam_class': np.float64(-0.00931986191210442), 'Macro_class': np.float64(0.28842331961400464), 'Nlen_freq': np.float64(-0.03983907946456676), 'Vlen_freq': np.float64(0.06059354704630172)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4308766640035368), 'Fam_class': np.float64(-0.020313601204661216), 'Macro_class': np.float64(0.2845237136429678), 'Nlen_freq': np.float64(-0.052646864029045636), 'Vlen_freq': np.float64(0.07214246545179512)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(19.50990345693703), 'Fam_class': np.float64(0.008685982606069466), 'Macro_class': np.float64(8.318801129716228), 'Nlen_freq': np.float64(0.15871522525840648), 'Vlen_freq': np.float64(0.36715779436523793)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.565469958281675), 'Fam_class': np.float64(0.04126423939020136), 'Macro_class': np.float64(8.095374362518553), 'Nlen_freq': np.float64(0.27716922920928194), 'Vlen_freq': np.float64(0.5204535321463452)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.003854422465778384</v>
+        <v>0.005256122809842889</v>
       </c>
       <c r="V5" t="n">
-        <v>3.545962318771366</v>
+        <v>4.788043470601331</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02914962989155186</v>
+        <v>0.008491799873005476</v>
       </c>
     </row>
   </sheetData>

--- a/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
+++ b/scripts/checks/results/HLR_results_13_>75_lg_families_Famfirst_tPBC.xlsx
@@ -562,57 +562,57 @@
         <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>0.2355842238404511</v>
+        <v>0.2353905796617167</v>
       </c>
       <c r="H2" t="n">
-        <v>363.662541775839</v>
+        <v>363.2715954217998</v>
       </c>
       <c r="I2" t="n">
-        <v>6.968483886006474e-71</v>
+        <v>8.095008422521239e-71</v>
       </c>
       <c r="J2" t="n">
-        <v>138.7796194903806</v>
+        <v>138.8147755746471</v>
       </c>
       <c r="K2" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L2" t="n">
-        <v>42.7702959072505</v>
+        <v>42.73513982298402</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1176098470257463</v>
+        <v>0.1176396403174976</v>
       </c>
       <c r="N2" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>{'const': 0.5682328519626636, 'N1ratio-ArgsPreds': -2.118622554728008}</t>
+          <t>{'const': 0.5677540716261412, 'N1ratio-ArgsPreds': -2.114660301017572}</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>{'const': 4.267556190895944e-115, 'N1ratio-ArgsPreds': 6.968483886004664e-71}</t>
+          <t>{'const': 4.817730324087699e-115, 'N1ratio-ArgsPreds': 8.095008422516971e-71}</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48537019257516306}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4851706706528301}</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.48537019257516234)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4853701925751624)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.48517067065282893)}</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(23.558422384045024)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(23.53905796617158)}</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -641,67 +641,67 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2357097723163037</v>
+        <v>0.2355149141067605</v>
       </c>
       <c r="H3" t="n">
-        <v>181.8038563721716</v>
+        <v>181.6072601386547</v>
       </c>
       <c r="I3" t="n">
-        <v>1.516253387259223e-69</v>
+        <v>1.762120913249163e-69</v>
       </c>
       <c r="J3" t="n">
-        <v>138.7568261752113</v>
+        <v>138.7922026666684</v>
       </c>
       <c r="K3" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L3" t="n">
-        <v>21.39654461120992</v>
+        <v>21.37885636548137</v>
       </c>
       <c r="M3" t="n">
-        <v>0.117690268172359</v>
+        <v>0.1177202736782599</v>
       </c>
       <c r="N3" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>{'const': 0.5715863027053953, 'N1ratio-ArgsPreds': -2.1038747852921906, 'Fam_class': -0.00012087906762604605}</t>
+          <t>{'const': 0.5710916823429171, 'N1ratio-ArgsPreds': -2.0999928344401866, 'Fam_class': -0.00012030183078327232}</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>{'const': 3.187628831203141e-106, 'N1ratio-ArgsPreds': 5.885558436980357e-65, 'Fam_class': 0.6599584798021098}</t>
+          <t>{'const': 3.7268642444079006e-106, 'N1ratio-ArgsPreds': 6.843036583685959e-65, 'Fam_class': 0.6615439713746508}</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.48199152199736595, 'Fam_class': -0.011703157297484928}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4818054849571873, 'Fam_class': -0.011647270916976241}</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4668105918264926), 'Fam_class': np.float64(-0.012815657774598577)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4665969704847937), 'Fam_class': np.float64(-0.012751929643546411)}</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.46146851927307075), 'Fam_class': np.float64(-0.011204841625506699)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4612573425654359), 'Fam_class': np.float64(-0.011150535639306203)}</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.295319428008046), 'Fam_class': np.float64(0.012554847585268758)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.275833607052785), 'Fam_class': np.float64(0.012433444504343779)}</t>
         </is>
       </c>
       <c r="U3" t="n">
-        <v>0.0001255484758526659</v>
+        <v>0.0001243344450437833</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1936720471736194</v>
+        <v>0.1917503865171438</v>
       </c>
       <c r="W3" t="n">
-        <v>0.659958479806684</v>
+        <v>0.6615439713788115</v>
       </c>
     </row>
     <row r="4">
@@ -726,67 +726,67 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3492609714554959</v>
+        <v>0.3492231561018947</v>
       </c>
       <c r="H4" t="n">
-        <v>210.7498327938573</v>
+        <v>210.714769456079</v>
       </c>
       <c r="I4" t="n">
-        <v>2.026215300087851e-109</v>
+        <v>2.096653304651497e-109</v>
       </c>
       <c r="J4" t="n">
-        <v>118.1416155781914</v>
+        <v>118.1484809524384</v>
       </c>
       <c r="K4" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L4" t="n">
-        <v>21.13609993981325</v>
+        <v>21.13381148173091</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1002899962463424</v>
+        <v>0.1002958242380632</v>
       </c>
       <c r="N4" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>{'const': 0.4028340233159108, 'N1ratio-ArgsPreds': -2.1345183214926675, 'Fam_class': 5.63257260560442e-05, 'Macro_class': 0.07763441457018583}</t>
+          <t>{'const': 0.4023285843356079, 'N1ratio-ArgsPreds': -2.131393139964399, 'Fam_class': 5.7577852847439596e-05, 'Macro_class': 0.07768887585019313}</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>{'const': 3.839914156116589e-54, 'N1ratio-ArgsPreds': 2.675478655394602e-76, 'Fam_class': 0.8244469015918944, 'Macro_class': 4.322341342706756e-43}</t>
+          <t>{'const': 4.454060390598872e-54, 'N1ratio-ArgsPreds': 2.768873736109304e-76, 'Fam_class': 0.8206291634372203, 'Macro_class': 3.847094873679871e-43}</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.4890118659626547, 'Fam_class': 0.005453291830213405, 'Macro_class': 0.33738002947098594}</t>
+          <t>{'N1ratio-ArgsPreds': -0.48900971879207555, 'Fam_class': 0.005574519078933, 'Macro_class': 0.33761670476963557}</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.5018946891585374), 'Fam_class': np.float64(0.006464479485016144), 'Macro_class': np.float64(0.38544880990627617)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.501851378168159), 'Fam_class': np.float64(0.006607466030716836), 'Macro_class': np.float64(0.38566609802934726)}</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4680968305790246), 'Fam_class': np.float64(0.005214900944498913), 'Macro_class': np.float64(0.33697358819231116)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.46805643617465736), 'Fam_class': np.float64(0.005330408162729559), 'Macro_class': np.float64(0.33720652721315586)}</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(21.911464279812808), 'Fam_class': np.float64(0.002719519186093565), 'Macro_class': np.float64(11.35511991392013)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(21.90768274445211), 'Fam_class': np.float64(0.0028413251181293913), 'Macro_class': np.float64(11.370824199515681)}</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>0.1135511991391922</v>
+        <v>0.1137082419951342</v>
       </c>
       <c r="V4" t="n">
-        <v>205.5560012823487</v>
+        <v>205.8283270620503</v>
       </c>
       <c r="W4" t="n">
-        <v>4.322341342706068e-43</v>
+        <v>3.847094873681829e-43</v>
       </c>
     </row>
     <row r="5">
@@ -811,67 +811,67 @@
         <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3545170942653388</v>
+        <v>0.3544719695755856</v>
       </c>
       <c r="H5" t="n">
-        <v>129.1783559725805</v>
+        <v>129.1528846382757</v>
       </c>
       <c r="I5" t="n">
-        <v>3.719729292359789e-109</v>
+        <v>3.875077188192401e-109</v>
       </c>
       <c r="J5" t="n">
-        <v>117.1873669267449</v>
+        <v>117.1955593103519</v>
       </c>
       <c r="K5" t="n">
         <v>181.5499153976311</v>
       </c>
       <c r="L5" t="n">
-        <v>12.87250969417726</v>
+        <v>12.87087121745585</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09964912153634767</v>
+        <v>0.09965608784893869</v>
       </c>
       <c r="N5" t="n">
         <v>0.1537255845873253</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>{'const': 0.4066187961530553, 'N1ratio-ArgsPreds': -2.0417210982057163, 'Fam_class': -0.00023527710716809958, 'Macro_class': 0.07082281520305496, 'Nlen_freq': -0.34722273935809433, 'Vlen_freq': 0.4723770185218674}</t>
+          <t>{'const': 0.4067219853575214, 'N1ratio-ArgsPreds': -2.038609946124176, 'Fam_class': -0.00023350941357385592, 'Macro_class': 0.07087917977348514, 'Nlen_freq': -0.35349458304769754, 'Vlen_freq': 0.4724557651202295}</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>{'const': 3.460694618048324e-21, 'N1ratio-ArgsPreds': 1.365843532947458e-66, 'Fam_class': 0.38608704188315124, 'Macro_class': 4.657879342781081e-32, 'Nlen_freq': 0.024814696161224423, 'Vlen_freq': 0.0021229591976609477}</t>
+          <t>{'const': 3.1418012839762172e-21, 'N1ratio-ArgsPreds': 1.520238562698623e-66, 'Fam_class': 0.38978795899572705, 'Macro_class': 4.286664584686109e-32, 'Nlen_freq': 0.023962418102818395, 'Vlen_freq': 0.0021242082214481773}</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': -0.46775229519262185, 'Fam_class': -0.02277884043748356, 'Macro_class': 0.3077784976252147, 'Nlen_freq': -0.08706200994837242, 'Vlen_freq': 0.12957205861125248}</t>
+          <t>{'N1ratio-ArgsPreds': -0.4677222882013982, 'Fam_class': -0.02260769752090193, 'Macro_class': 0.3080234441548966, 'Nlen_freq': -0.08760704159967526, 'Vlen_freq': 0.12961130072052526}</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.47262480075837676), 'Fam_class': np.float64(-0.02527585041960119), 'Macro_class': np.float64(0.33382556693384297), 'Nlen_freq': np.float64(-0.06538824844991198), 'Vlen_freq': np.float64(0.08943443504502634)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.4724755582836825), 'Fam_class': np.float64(-0.025079553115110058), 'Macro_class': np.float64(0.33401223285199133), 'Nlen_freq': np.float64(-0.06577945018780361), 'Vlen_freq': np.float64(0.08942934560016297)}</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(-0.4308766640035368), 'Fam_class': np.float64(-0.020313601204661216), 'Macro_class': np.float64(0.2845237136429678), 'Nlen_freq': np.float64(-0.052646864029045636), 'Vlen_freq': np.float64(0.07214246545179512)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(-0.43071654929322734), 'Fam_class': np.float64(-0.020156446555294753), 'Macro_class': np.float64(0.2847127349342342), 'Nlen_freq': np.float64(-0.05296505316951929), 'Vlen_freq': np.float64(0.07214084843595235)}</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>{'N1ratio-ArgsPreds': np.float64(18.565469958281675), 'Fam_class': np.float64(0.04126423939020136), 'Macro_class': np.float64(8.095374362518553), 'Nlen_freq': np.float64(0.27716922920928194), 'Vlen_freq': np.float64(0.5204535321463452)}</t>
+          <t>{'N1ratio-ArgsPreds': np.float64(18.551674583506514), 'Fam_class': np.float64(0.04062823377364537), 'Macro_class': np.float64(8.10613414337315), 'Nlen_freq': np.float64(0.28052968572500053), 'Vlen_freq': np.float64(0.5204302013059049)}</t>
         </is>
       </c>
       <c r="U5" t="n">
-        <v>0.005256122809842889</v>
+        <v>0.005248813473690883</v>
       </c>
       <c r="V5" t="n">
-        <v>4.788043470601331</v>
+        <v>4.781050825168803</v>
       </c>
       <c r="W5" t="n">
-        <v>0.008491799873005476</v>
+        <v>0.008550905490498218</v>
       </c>
     </row>
   </sheetData>
